--- a/AAII_Financials/Quarterly/NVO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>NVO</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11993900</v>
+      </c>
+      <c r="E8" s="3">
         <v>14936800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12442300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11778500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12099700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11314100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11894700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10665500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9778400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9451500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9767300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8330200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7959200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7782800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7138300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6603400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6023500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6116400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5577500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5152000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4698400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4639600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4310000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4314600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4401600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5144300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5090100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4988700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4752300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4708800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4725900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4125200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4028600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4048700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4001100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4305400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4478600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4654900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4334600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2613100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2097800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2227700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2273400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2022400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1867600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1674500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1691300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1476100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1434200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1418900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1377700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1151500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1193200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1226300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1043400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>885900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1006600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>908100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>876300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>788800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>797600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>753600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>719200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>700000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>817900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>852900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>836200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>767200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>760700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>739600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>656000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>639700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>631000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>706600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>642300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>662800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>669100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>774100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>627400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9380800</v>
+      </c>
+      <c r="E10" s="3">
         <v>12839100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10214600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9505200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10077400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9446400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10220200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8974200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8302300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8017300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8348400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6952600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6807700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6589600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5912000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5560000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5137600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5109800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4669400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4275700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3909600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3842000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3556500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3595500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3701600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4326300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4237200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4152500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3985100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3948100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3986300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3469100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3388900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3417700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3501700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3358900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3642600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3809500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3880800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>3707200</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,130 +1249,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1751100</v>
+      </c>
+      <c r="E12" s="3">
         <v>1586500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1992000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1805000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1840400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1493500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>806800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1419100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1503700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1244700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1348300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1152900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1044700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>981200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1200100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>816300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>747800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>757600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>819500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>615000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>560800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>541300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>601200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>545600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>482800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>573600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>688400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>593300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>562800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>430500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>722300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>541500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>484500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>499300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>598800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>500300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>513300</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>517700</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>703600</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>544300</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1480,43 +1497,46 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>967000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>539900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1503700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3">
         <v>1468600</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>818900</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>309500</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
@@ -1527,8 +1547,8 @@
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1563,8 +1583,8 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
@@ -1572,23 +1592,23 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-18300</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>10</v>
+      <c r="AL14" s="3">
+        <v>0</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>10</v>
@@ -1599,56 +1619,59 @@
       <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AP14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>550900</v>
+      </c>
+      <c r="E15" s="3">
         <v>541900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>222300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>508500</v>
       </c>
-      <c r="G15" s="3">
-        <v>660900</v>
-      </c>
       <c r="H15" s="3">
+        <v>589400</v>
+      </c>
+      <c r="I15" s="3">
         <v>544600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>80000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>302100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>292700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>312000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>216000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>358100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>319100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>250700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1724,8 +1747,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6891600</v>
+      </c>
+      <c r="E17" s="3">
         <v>5739600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6902000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6554400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6833800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5693600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5328600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5607000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5233500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4845600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5483000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4513000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4457700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4135900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4602100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3678400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3338900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3330100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3593700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2946500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2596900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2583300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2810900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2527800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2371700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2668600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3225800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2860100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2623900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2419800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3011900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2369900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2234700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2177200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2697900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2190500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2293000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2355200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2891000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2379600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5102200</v>
+      </c>
+      <c r="E18" s="3">
         <v>9197200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5540300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5224100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5265900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5620400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6566200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5058500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4545000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4605900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4284300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3817300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3501500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3646900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2536200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2925100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2684500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2786300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1983700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2205500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2101600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2056300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1499100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1786800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2029900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2475600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1864300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2128700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2128400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2289100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1714000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1755300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1793900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1871400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1510500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1810700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2012500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2123500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1763900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1955000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,296 +2086,303 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3">
         <v>-394000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-461900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-240000</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>254700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>191000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-84100</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-51300</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-53600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>39400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-114400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-311900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-233000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-178700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-75800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-19800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>19600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>131200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>110500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-61900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-194500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-124700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-133800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-206800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-163500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-65600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-100300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>174500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>78800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>62800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-111700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-76500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-41600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-18700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5653100</v>
+      </c>
+      <c r="E21" s="3">
         <v>10133200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6224500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5972700</v>
       </c>
-      <c r="G21" s="3">
-        <v>5926800</v>
-      </c>
       <c r="H21" s="3">
+        <v>5855400</v>
+      </c>
+      <c r="I21" s="3">
         <v>5910400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6455100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5444700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4837600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4906900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4551600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4175400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3874200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3858200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2723800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2909000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2690400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2847700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2210900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2380800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2294300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2376500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1794500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2067700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2137900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2446000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1959100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2340100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2097200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2295700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1909300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1771300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1950000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2156000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1725300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1979700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2030500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2158400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1898000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2052200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="3">
+        <v>229200</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-692700</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>780500</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-85100</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>224400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>289000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>-311600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>307500</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2419,252 +2459,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4106800</v>
+      </c>
+      <c r="E23" s="3">
         <v>9591200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5374300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4008700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5322000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5365700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4936100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5142600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3639500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4616300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4096000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3980400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3555100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3607500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2421800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2613200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2451600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2607600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1907900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2185600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2121200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2187500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1609600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1770500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1968000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2281100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1739600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1994900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1921600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2125600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1648300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1655000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1837100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2046000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1589200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1873500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1900700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2047000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1722400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1936300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>899400</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1146700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>865800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1149600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1159000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1017200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1059400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>758900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>941700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>838900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>792200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>707400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>718000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>404300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>525600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>507500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>539700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>323200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>432900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>397300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>455000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>360000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>333800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>409400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>474400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>370900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>315200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>403500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>446400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>297700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>312200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>316800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>429700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>348500</v>
-      </c>
-      <c r="AL24" s="3">
-        <v>404700</v>
       </c>
       <c r="AM24" s="3">
         <v>404700</v>
       </c>
       <c r="AN24" s="3">
+        <v>404700</v>
+      </c>
+      <c r="AO24" s="3">
         <v>448300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>353100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>393200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3207400</v>
+      </c>
+      <c r="E26" s="3">
         <v>7490900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4227600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3142900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4172400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4206700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3919000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4083200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2880700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3674600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3257000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3188200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2847700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2889600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2017500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2087600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1944000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2067800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1584800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1752800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1723900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1732500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1249600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1436700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1558600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1806700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1368700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1679700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1518100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1679100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1350600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1342800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1520300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1616300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1240800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1468800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1496000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1598700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1369300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1543100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3207400</v>
+      </c>
+      <c r="E27" s="3">
         <v>7490900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4227600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3142900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4172400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4206700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3919000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4083200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2880700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3674600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3257000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3188200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2847700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2889600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2017500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2087600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1944000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2067800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1584800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1752800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1723900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1732500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1249600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1436700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1558600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1806700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1368700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1679700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1518100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1679100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1350600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1342800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1520300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1616300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1240800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1468800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1496000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1598700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1369300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1543100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,252 +3584,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3">
         <v>394000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>461900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>240000</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-254700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-191000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>84100</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>51300</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="O32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>53600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-39400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>114400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>311900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>233000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>178700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>75800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>19800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-19600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-131200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-110500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>16300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>61900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>194500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>124700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>133800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>206800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>163500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>65600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>100300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-43200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-174500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-78800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-62800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>111700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>76500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>41600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3207400</v>
+      </c>
+      <c r="E33" s="3">
         <v>7490900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4227600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3142900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4172400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4206700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3919000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4083200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2880700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3674600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3257000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3188200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2847700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2889600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2017500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2087600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1944000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2067800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1584800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1752800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1723900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1732500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1249600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1436700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1558600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1806700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1368700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1679700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1518100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1679100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1350600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1342800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1520300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1616300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1240800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1468800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1496000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1598700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1369300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1543100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3207400</v>
+      </c>
+      <c r="E35" s="3">
         <v>7490900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4227600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3142900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4172400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4206700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3919000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4083200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2880700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3674600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3257000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3188200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2847700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2889600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2017500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2087600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1944000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2067800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1584800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1752800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1723900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1732500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1249600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1436700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1558600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1806700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1368700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1679700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1518100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1679100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1350600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1342800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1520300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1616300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1240800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1468800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1496000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1598700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1369300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1543100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,198 +4306,202 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6797400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3259200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4160400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5040300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2902300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5641700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2173300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8527800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7589000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>914600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2134300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4275500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3162300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2178200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1878100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4125100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3322000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1949100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1559800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4265600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3445400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>780000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1710800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3554700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3648800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1482900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2429900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3090600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2287400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1455700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2485700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2437000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2703600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1580500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2834200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2876600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3206300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2638700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2942000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2288300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E42" s="3">
         <v>77000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>78300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>78400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>78600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>378500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1478900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2671600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1412700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>430900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2348700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2475200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2174300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1871800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1621000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1305400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1208500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>982600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>984300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>852900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>424800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>272200</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>10</v>
@@ -4428,8 +4518,8 @@
       <c r="AD42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -4443,883 +4533,907 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK42" s="3">
-        <v>0</v>
-      </c>
       <c r="AL42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AM42" s="3">
         <v>500</v>
       </c>
       <c r="AN42" s="3">
+        <v>500</v>
+      </c>
+      <c r="AO42" s="3">
         <v>157900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>316200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>321400</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16581900</v>
+      </c>
+      <c r="E43" s="3">
         <v>15468300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14021000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14511600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13514400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12513600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12258700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11909500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10937900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10377300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11161000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8788800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10336800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8447000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8535500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7754700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6807900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6427000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6809300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5127400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4297700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4655100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4316200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3961200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4422100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5401500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4577400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4370000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4271900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4269800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4274000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3204800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3282600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3203900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3540700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3029800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3135300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3547400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3808800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3177600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7847200</v>
+      </c>
+      <c r="E44" s="3">
         <v>7922000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7801300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7462800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7187100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6209000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5670700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5675000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5223400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4859600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4717500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4189000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4107100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3735600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3619900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3365300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3168400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2952500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2854900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2733400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2676500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2560100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2485900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2525800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2612400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2621300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2770000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2885000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2710200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2706900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2596600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2365800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2371500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2385400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2311200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2289700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2259300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2368100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2257400</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2243400</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>588300</v>
+      </c>
+      <c r="E45" s="3">
         <v>628000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1050500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1480300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1932600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>525400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>878200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>404700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>339100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>255700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>347600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>440500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>381400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>384400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>404800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>764700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>525100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>281700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>245900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>212900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>125800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>158200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>312700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>235500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>110000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>90800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>29500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>100800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>21200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>45200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>32400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>36300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>94500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>334400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>346400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>387000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>264700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>47500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>83300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>87800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31891100</v>
+      </c>
+      <c r="E46" s="3">
         <v>27354600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27111500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28573300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25614900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25268200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22459800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29188700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25502100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16838100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20709100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20169100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20161900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16617000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16059200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17315300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15031800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12592900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12454100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13192100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10970200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8425600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8825600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10277300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10793300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9596500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9806800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10446400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9290700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8477500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9388700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8043900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8452200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7504200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9032400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>8583500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>8866200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>8759600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>9407800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>8118600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>356100</v>
+      </c>
+      <c r="E47" s="3">
         <v>345700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>394100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>428100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>415300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>391200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>371600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>306200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>238400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>238800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>246600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>208600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>216800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>176600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>229900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>215400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>218100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>220900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>248500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>305200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>320200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>315700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>311400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>306200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>364800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>369500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>415900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>339800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>331900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>274300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>281800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>229400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>223600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>234500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>264900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>332700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>301000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>321100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>345800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>315000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35415200</v>
+      </c>
+      <c r="E48" s="3">
         <v>33935200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32759300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30358100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28457000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24975600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22444800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17922400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15801200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14207100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13489300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11554200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10996900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10210600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9896000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9222900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8693400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8207200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8055200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7645600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7405200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7058600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6741600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6965000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7408100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7724100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7937500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8287900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7626800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7612000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6658600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5877500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5581400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5432400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5299000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4980500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4794000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>4894800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4750500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4442600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18651700</v>
+      </c>
+      <c r="E49" s="3">
         <v>20041100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20445800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16744500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16981500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15848000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15384400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8149400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7974000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8625800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8958000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7904000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7438700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7363100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7631700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6800200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6508800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6307400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6281400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2968700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2882700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2794000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2770300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1313500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>848600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>886600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>916200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>829300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>933500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>852300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>817800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>685000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>616900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>606600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>499900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>393100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>397900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>436200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>427200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>448500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>982300</v>
+      </c>
+      <c r="E52" s="3">
         <v>924400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>921900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>797600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>698800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>584900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>557500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>367300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>312900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>291000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>212100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>61000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>49500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1993000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1638000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1504800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1358900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1261800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1066200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>902800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>811400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>786600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>662000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>552700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>596700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>647100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>677700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>472600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>489200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>459800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>304800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>302400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>287800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>291800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>427100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>347900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>418400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>422300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>423600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>90913700</v>
+      </c>
+      <c r="E54" s="3">
         <v>86270600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>85350100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80479100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>75906200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70874900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64639800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>59442400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>53070600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43233300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46637400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42565500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41152200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36462700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35809800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35191800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31956900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>28687200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>28300900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>25177800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22481100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19405400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19435500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19524000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19967600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19173200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19723600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20581100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>18655600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>17705300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>17606700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15140600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15176400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14065500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15388100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>14716900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>14707000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>14830100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15353600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>13748200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,589 +6146,602 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2229700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2283600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3106200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3755300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4440500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2836400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2379400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3601300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4275600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1881100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3797300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2851800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2607300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1465700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2313600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1204300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2139000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>971900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1290600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1283900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1083000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>933300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>766700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>854200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1314500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>811500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>998300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>971200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>833700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>678700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1073900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>720100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>857000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>618900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>843400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>681000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>640000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>595300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>946200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>702400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2801500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4197700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1889200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1890500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1883400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3247400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1820400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>825600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>783300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1470000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>960700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>938000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>921800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>182400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>217600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>265600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>183300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>203100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1991000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>195300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>185000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>936500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1000300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>204800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>206500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>188900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>231400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>233300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>198600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>179100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>81900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>50100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>36300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>34300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>254700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>39100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>253000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>96500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>36000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>71800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>31503400</v>
+      </c>
+      <c r="E59" s="3">
         <v>28253700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28764700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31171300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26346700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28127300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25876600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26735700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21938700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20600700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20312400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20684500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19427600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17596600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15419900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17406900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13684000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12736900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11198000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11295700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9083900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8064900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7657300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8838900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8348900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8595100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8031700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9190400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7922200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7945400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7453600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6573900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6335600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5987000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5976300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6064300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>5695500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>7006000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>6484700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>5772900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36534600</v>
+      </c>
+      <c r="E60" s="3">
         <v>34735000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33904300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36817000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32670500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34211100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30209600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31162600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26997600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23951800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25159300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24474300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22956700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19244700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17951100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18876800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16006300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13912000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14479600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12774900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10351900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9934700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9424300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9898000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9869900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9595600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9261500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10394800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8954500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8803200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8609400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7344100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7228800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6640200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7074400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6784400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>6588500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>7697800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>7466900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>6547000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18611500</v>
+      </c>
+      <c r="E61" s="3">
         <v>18384600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18698800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14009900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13744600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13954400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12448700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7695300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7414700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2424600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3044200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2826000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2845800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3539000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3609500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3497800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3529300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3504700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1885800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1793100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1772200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>388700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>388500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>367700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>401200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>435200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>472500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>482300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>471000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>515100</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -6626,130 +6769,136 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1181100</v>
+      </c>
+      <c r="E62" s="3">
         <v>924700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1066000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1388000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1362400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1253900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1171400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1145800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1083900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1040200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1014100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>870300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>867900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>782600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1857300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1704700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1553600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1586200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1642000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1048000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1034500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1053400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1130100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>947300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>887200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>881400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>946400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>978900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>831000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>780000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>757600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>736700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>733200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>774600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>824500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>874700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>836600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>788500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>760900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>695900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57100100</v>
+      </c>
+      <c r="E66" s="3">
         <v>54943900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54843800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53788900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>49447300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50801800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44720700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>41416800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36904100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28927700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30834700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29375900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27890800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24814200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23417900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>24079300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>21089200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>19002900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18007400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15616000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13158600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11376800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10943000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11213000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11158300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10912200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10680300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11856000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10256500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10098300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9366900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>8080800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7962000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7414800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7898900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7659100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7425100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8486300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8227800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7242900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34254800</v>
+      </c>
+      <c r="E72" s="3">
         <v>31844300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30703000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26475500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25890100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19896200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20052600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18197300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16113000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14325700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15547300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13011400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12916200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11239600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11967200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11047000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10801600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9618100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10227200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9495500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9257200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7965300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8527900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8341000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8823100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8585900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9152900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8972100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8557000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7949600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8599500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>7372400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>7545400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6569100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7344900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6861500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>7159900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6629500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7493800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>6616100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33813600</v>
+      </c>
+      <c r="E76" s="3">
         <v>31326700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30506300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26690200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26458900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20073100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19919000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18025600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16166400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14305600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15802700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13189600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13261300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11648500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12391800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11112500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10867800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9684400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10293500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9561800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9322500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8028600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8492500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8311000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8809300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8261000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9043300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8725100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8399100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7607000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8239800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7059800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7214400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6650700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7489200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7057900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>7281900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6343800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7125800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6505300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3207400</v>
+      </c>
+      <c r="E81" s="3">
         <v>7490900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4227600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3142900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4172400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4206700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3919000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4083200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2880700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3674600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3257000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3188200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2847700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2889600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2017500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2087600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1944000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2067800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1584800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1752800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1723900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1732500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1249600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1436700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1558600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1806700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1368700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1679700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1518100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1679100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1350600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1342800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1520300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1616300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1240800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1468800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1496000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1598700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1369300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1543100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>334200</v>
+      </c>
+      <c r="E83" s="3">
         <v>309500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>208800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>217200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>216400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>227200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>97100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>358100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>319100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>250700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>148100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>268900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>230100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>246200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>302100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>295800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>238800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>240100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>302900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>195100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>173100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>189000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>184900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>297200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>169900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>164900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>219500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>345200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>175600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>170100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>261000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>116300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>112900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>110000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>136100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>106100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>129700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>111400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>175700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>115900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8435000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3715400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1197800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7243300</v>
       </c>
-      <c r="G89" s="3">
-        <v>6420900</v>
-      </c>
       <c r="H89" s="3">
+        <v>6576600</v>
+      </c>
+      <c r="I89" s="3">
         <v>3583100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1707700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6558300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7255900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2070300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1416400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5810500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4188800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4348000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1054000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3512700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3497600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3432200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-439000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3110600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3591300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1544700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>23100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2442300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3558800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1520400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>811000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2749700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2379500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1589900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1243600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1726500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2318000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1475600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>906900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1942500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1521000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1904300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1755600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2390900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1936900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1744900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2897200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2140900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2308100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1944700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2235200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1812600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1504300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1225600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1395000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-826600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-861600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-684400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6173000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4225000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2575000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1780000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2314000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1688000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-243000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-192400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-203600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-195500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-253200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-299400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-368100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-339700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-425000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-438700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-359300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-350600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-311700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-379500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-292100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-233800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-269500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-435200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-410100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1950500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1806800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6730500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2423200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-2243100</v>
-      </c>
       <c r="H94" s="3">
+        <v>-2222600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-866300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12662800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3126500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2978500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>572200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2182500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1878300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1361000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-969400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2055800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-718900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-613100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-277500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2997700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-670400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-410400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-477800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1730000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-845800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-200500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-319800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-503900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-402200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-448200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-486500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-651500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-425600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-373800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-387000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-475500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-299300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-109000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-108900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-429900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-421400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,130 +10456,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>5447600</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>2617700</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5110900</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>2330600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>4130200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>1904900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>2674200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-1393100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-2283200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-1160100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1852200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1056100</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1906000</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1169900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1978800</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1075500</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-1775500</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-1111900</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-1196300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2923600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2689400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4632500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2685700</v>
       </c>
-      <c r="G100" s="3">
-        <v>-7278100</v>
-      </c>
       <c r="H100" s="3">
+        <v>-7454200</v>
+      </c>
+      <c r="I100" s="3">
         <v>669100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5113500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2752100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2396900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3815700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2812900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1845300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3007300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1138200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2110500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1522600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2784500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>661900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1696700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-545500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1986700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-48300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1491900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1126700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2051500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-816700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1649700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1067400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2174300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-660000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1606100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-797100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2125400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-691900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1749100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-861100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2160500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-644600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1762800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-127500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>99500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-52000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-31000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>59300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-38400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-121300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>58400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>30700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-125300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>64200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>31800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>43700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>17600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>21100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-14400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>12400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-9500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>12500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-10100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>8300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3568900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-823300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-883500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2144200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3227800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3373500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5742100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>627700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6680400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1166900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2297300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1178500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>973000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>332900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2265200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>747500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1393700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>362200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2731200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>761200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2637500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-898600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1775500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>85700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2220600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-865300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-525200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>710200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>854400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1058300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-69100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-309500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1155600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1033300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-257800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-115900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>525300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-363800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>689500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>207800</v>
       </c>
     </row>
